--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/34.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/34.xlsx
@@ -426,13 +426,13 @@
         <v>-15.42526817667586</v>
       </c>
       <c r="E2">
-        <v>-4.961624131112664</v>
+        <v>-5.17865018889158</v>
       </c>
       <c r="F2">
-        <v>3.689862216067151</v>
+        <v>5.350803471337579</v>
       </c>
       <c r="G2">
-        <v>-17.4812450022975</v>
+        <v>-20.05783191655296</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.4878310491617</v>
       </c>
       <c r="E3">
-        <v>-6.314009415548633</v>
+        <v>-6.228208222789001</v>
       </c>
       <c r="F3">
-        <v>2.940574079008498</v>
+        <v>4.974245874107785</v>
       </c>
       <c r="G3">
-        <v>-16.74914130942981</v>
+        <v>-19.42049433622579</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.30162774990383</v>
       </c>
       <c r="E4">
-        <v>-7.339653258637691</v>
+        <v>-7.848537935846283</v>
       </c>
       <c r="F4">
-        <v>3.482677588218162</v>
+        <v>5.042466899932741</v>
       </c>
       <c r="G4">
-        <v>-16.48340797659564</v>
+        <v>-18.28244596688589</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.00590939184798</v>
       </c>
       <c r="E5">
-        <v>-6.594521461638878</v>
+        <v>-8.212890858950841</v>
       </c>
       <c r="F5">
-        <v>3.84363702725324</v>
+        <v>5.389967025407134</v>
       </c>
       <c r="G5">
-        <v>-16.30566195797117</v>
+        <v>-17.54762840501574</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.63200737513832</v>
       </c>
       <c r="E6">
-        <v>-8.554288983063072</v>
+        <v>-8.252603865638852</v>
       </c>
       <c r="F6">
-        <v>3.791352133523341</v>
+        <v>5.278574804017878</v>
       </c>
       <c r="G6">
-        <v>-15.3211358135671</v>
+        <v>-17.05270563676151</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.266823214505983</v>
       </c>
       <c r="E7">
-        <v>-10.40704070828041</v>
+        <v>-8.978709801558626</v>
       </c>
       <c r="F7">
-        <v>2.813260636137436</v>
+        <v>5.370823454728437</v>
       </c>
       <c r="G7">
-        <v>-15.32553622357542</v>
+        <v>-16.23574752319345</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.947709660237337</v>
       </c>
       <c r="E8">
-        <v>-9.608290953078059</v>
+        <v>-9.97441729741832</v>
       </c>
       <c r="F8">
-        <v>3.874757133841612</v>
+        <v>5.523388849506438</v>
       </c>
       <c r="G8">
-        <v>-12.74540130742064</v>
+        <v>-15.89773050486513</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.728605766819992</v>
       </c>
       <c r="E9">
-        <v>-10.16597586335339</v>
+        <v>-10.41018884246463</v>
       </c>
       <c r="F9">
-        <v>3.819978854229286</v>
+        <v>5.258889481057751</v>
       </c>
       <c r="G9">
-        <v>-13.66908665987341</v>
+        <v>-14.55577253998092</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.626684688089105</v>
       </c>
       <c r="E10">
-        <v>-12.38996653605185</v>
+        <v>-11.55800354988484</v>
       </c>
       <c r="F10">
-        <v>3.915754693340965</v>
+        <v>5.625294607398834</v>
       </c>
       <c r="G10">
-        <v>-13.01815232171572</v>
+        <v>-13.71229056673945</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.646008582903126</v>
       </c>
       <c r="E11">
-        <v>-10.29320949228951</v>
+        <v>-11.68991369477272</v>
       </c>
       <c r="F11">
-        <v>3.810237253572364</v>
+        <v>5.48639893150183</v>
       </c>
       <c r="G11">
-        <v>-12.13065841615726</v>
+        <v>-13.74244075064992</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.783820324066751</v>
       </c>
       <c r="E12">
-        <v>-12.50810047897527</v>
+        <v>-12.04762978618021</v>
       </c>
       <c r="F12">
-        <v>4.139430459444887</v>
+        <v>5.856906133221575</v>
       </c>
       <c r="G12">
-        <v>-11.49465362094386</v>
+        <v>-13.59270932686039</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.012381704366077</v>
       </c>
       <c r="E13">
-        <v>-12.22721879707712</v>
+        <v>-13.04431328670123</v>
       </c>
       <c r="F13">
-        <v>4.117768651861681</v>
+        <v>6.089983869347273</v>
       </c>
       <c r="G13">
-        <v>-10.93089465542804</v>
+        <v>-12.37194082052336</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.314477506082184</v>
       </c>
       <c r="E14">
-        <v>-12.88923652904346</v>
+        <v>-13.90059332517511</v>
       </c>
       <c r="F14">
-        <v>4.949568809178388</v>
+        <v>6.279380135588545</v>
       </c>
       <c r="G14">
-        <v>-9.96212043851445</v>
+        <v>-11.76194817904352</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.662773470174712</v>
       </c>
       <c r="E15">
-        <v>-14.69627801041974</v>
+        <v>-14.8958148953098</v>
       </c>
       <c r="F15">
-        <v>4.870080329940553</v>
+        <v>6.41260646498079</v>
       </c>
       <c r="G15">
-        <v>-10.26612859242664</v>
+        <v>-10.64342165238367</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.031167415661076</v>
       </c>
       <c r="E16">
-        <v>-16.23493482277426</v>
+        <v>-15.75357347701531</v>
       </c>
       <c r="F16">
-        <v>5.157394593397144</v>
+        <v>6.924655148082082</v>
       </c>
       <c r="G16">
-        <v>-8.744530513717105</v>
+        <v>-10.74450446146239</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.4078760347148989</v>
       </c>
       <c r="E17">
-        <v>-17.12490986472647</v>
+        <v>-16.3382334948454</v>
       </c>
       <c r="F17">
-        <v>5.220690146645055</v>
+        <v>6.756200009783581</v>
       </c>
       <c r="G17">
-        <v>-9.230964445933333</v>
+        <v>-9.801337732870739</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2214442819217979</v>
       </c>
       <c r="E18">
-        <v>-16.75221314007034</v>
+        <v>-17.31794282068185</v>
       </c>
       <c r="F18">
-        <v>5.325024677762458</v>
+        <v>6.994367235232078</v>
       </c>
       <c r="G18">
-        <v>-7.611694495953366</v>
+        <v>-9.313379125813302</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.8516621676689035</v>
       </c>
       <c r="E19">
-        <v>-18.13140325039675</v>
+        <v>-18.26619157073273</v>
       </c>
       <c r="F19">
-        <v>5.544997641575867</v>
+        <v>7.296958250331097</v>
       </c>
       <c r="G19">
-        <v>-7.37402797284596</v>
+        <v>-8.450684683125827</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.472651000615978</v>
       </c>
       <c r="E20">
-        <v>-19.53106038613192</v>
+        <v>-18.72957781787783</v>
       </c>
       <c r="F20">
-        <v>5.67151585174024</v>
+        <v>7.120872191518007</v>
       </c>
       <c r="G20">
-        <v>-7.151443721241415</v>
+        <v>-8.249481124350204</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.070604946094936</v>
       </c>
       <c r="E21">
-        <v>-19.82512020756375</v>
+        <v>-19.18472409375446</v>
       </c>
       <c r="F21">
-        <v>5.78629443907214</v>
+        <v>7.045156097432521</v>
       </c>
       <c r="G21">
-        <v>-7.216895088140625</v>
+        <v>-7.851672833396204</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.623580257244392</v>
       </c>
       <c r="E22">
-        <v>-19.12889247391479</v>
+        <v>-19.07640834240294</v>
       </c>
       <c r="F22">
-        <v>5.826032880119238</v>
+        <v>7.011406752707663</v>
       </c>
       <c r="G22">
-        <v>-6.174933868104357</v>
+        <v>-7.591688360151665</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.116370231057072</v>
       </c>
       <c r="E23">
-        <v>-19.79446535477519</v>
+        <v>-19.70723545731982</v>
       </c>
       <c r="F23">
-        <v>5.885952007833337</v>
+        <v>7.145567480530266</v>
       </c>
       <c r="G23">
-        <v>-6.773791683903104</v>
+        <v>-6.81902022319955</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.535219754325903</v>
       </c>
       <c r="E24">
-        <v>-19.49118540420224</v>
+        <v>-19.24901165185148</v>
       </c>
       <c r="F24">
-        <v>5.95102358079285</v>
+        <v>7.138537954750109</v>
       </c>
       <c r="G24">
-        <v>-6.494961550827614</v>
+        <v>-6.66131297468417</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.872780561445675</v>
       </c>
       <c r="E25">
-        <v>-21.63685481773708</v>
+        <v>-20.01129205841051</v>
       </c>
       <c r="F25">
-        <v>5.17786355192032</v>
+        <v>6.625400796881538</v>
       </c>
       <c r="G25">
-        <v>-6.729918121049446</v>
+        <v>-6.950452938149967</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.134749485111745</v>
       </c>
       <c r="E26">
-        <v>-20.35666480576061</v>
+        <v>-20.23242564218969</v>
       </c>
       <c r="F26">
-        <v>6.24919111396092</v>
+        <v>6.957773276846006</v>
       </c>
       <c r="G26">
-        <v>-5.807108673406996</v>
+        <v>-6.180659230992668</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.328729273595085</v>
       </c>
       <c r="E27">
-        <v>-20.60275088317935</v>
+        <v>-20.28750553077956</v>
       </c>
       <c r="F27">
-        <v>5.580678739084052</v>
+        <v>7.07856581152223</v>
       </c>
       <c r="G27">
-        <v>-5.487676240450513</v>
+        <v>-6.655911344125157</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.470483766472107</v>
       </c>
       <c r="E28">
-        <v>-20.46040371823217</v>
+        <v>-20.01380890447336</v>
       </c>
       <c r="F28">
-        <v>5.998419450111427</v>
+        <v>6.904903555729731</v>
       </c>
       <c r="G28">
-        <v>-6.482751098374977</v>
+        <v>-6.324250183503898</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.5769733329593</v>
       </c>
       <c r="E29">
-        <v>-18.98179818842334</v>
+        <v>-20.40397403596173</v>
       </c>
       <c r="F29">
-        <v>5.385876547172109</v>
+        <v>6.629696710232457</v>
       </c>
       <c r="G29">
-        <v>-6.610194595590173</v>
+        <v>-6.556110410640669</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.660906346540117</v>
       </c>
       <c r="E30">
-        <v>-19.62623953006301</v>
+        <v>-19.6725395299122</v>
       </c>
       <c r="F30">
-        <v>5.254999467734204</v>
+        <v>6.78865378789046</v>
       </c>
       <c r="G30">
-        <v>-5.452389416557025</v>
+        <v>-6.692487875846655</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.737120468321392</v>
       </c>
       <c r="E31">
-        <v>-20.03757357967403</v>
+        <v>-19.88550790022676</v>
       </c>
       <c r="F31">
-        <v>5.410749106808567</v>
+        <v>6.870885819966366</v>
       </c>
       <c r="G31">
-        <v>-6.393706432605876</v>
+        <v>-6.332283444610754</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.810529393734583</v>
       </c>
       <c r="E32">
-        <v>-19.22711176853566</v>
+        <v>-19.70368446163709</v>
       </c>
       <c r="F32">
-        <v>5.801085767416528</v>
+        <v>6.947642343509768</v>
       </c>
       <c r="G32">
-        <v>-6.125306224171884</v>
+        <v>-6.89028571830317</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.88323763159363</v>
       </c>
       <c r="E33">
-        <v>-20.72857657347635</v>
+        <v>-19.06230818995514</v>
       </c>
       <c r="F33">
-        <v>5.851945869213612</v>
+        <v>6.903376046238969</v>
       </c>
       <c r="G33">
-        <v>-6.728988695975009</v>
+        <v>-7.074288386340243</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.954055770661184</v>
       </c>
       <c r="E34">
-        <v>-20.24715292954753</v>
+        <v>-18.64555835277655</v>
       </c>
       <c r="F34">
-        <v>5.193493188076341</v>
+        <v>6.720684585755954</v>
       </c>
       <c r="G34">
-        <v>-6.593733850943203</v>
+        <v>-6.863032155516539</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.014195685029188</v>
       </c>
       <c r="E35">
-        <v>-17.1788434669907</v>
+        <v>-18.11581624829467</v>
       </c>
       <c r="F35">
-        <v>5.525292437798072</v>
+        <v>7.420495994580199</v>
       </c>
       <c r="G35">
-        <v>-6.930579950322413</v>
+        <v>-7.708325985504243</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.06040109396094</v>
       </c>
       <c r="E36">
-        <v>-18.15248079787025</v>
+        <v>-17.80192068957545</v>
       </c>
       <c r="F36">
-        <v>5.949575594572757</v>
+        <v>7.285665945896135</v>
       </c>
       <c r="G36">
-        <v>-6.676961777763304</v>
+        <v>-7.945714464312696</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.08442708471501</v>
       </c>
       <c r="E37">
-        <v>-17.1981143675379</v>
+        <v>-17.96029509702513</v>
       </c>
       <c r="F37">
-        <v>5.884583544883912</v>
+        <v>7.513576326163168</v>
       </c>
       <c r="G37">
-        <v>-7.91006866303793</v>
+        <v>-7.667444335951999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.08167595821465</v>
       </c>
       <c r="E38">
-        <v>-16.81151684457756</v>
+        <v>-17.45626137064394</v>
       </c>
       <c r="F38">
-        <v>6.049309373135011</v>
+        <v>7.600702352854815</v>
       </c>
       <c r="G38">
-        <v>-6.81336796115979</v>
+        <v>-7.796885052779396</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.051563174518019</v>
       </c>
       <c r="E39">
-        <v>-16.11751938541004</v>
+        <v>-16.25302205809389</v>
       </c>
       <c r="F39">
-        <v>5.459293093347424</v>
+        <v>8.138839638939874</v>
       </c>
       <c r="G39">
-        <v>-7.97069929004965</v>
+        <v>-8.170375563239473</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.990799845161387</v>
       </c>
       <c r="E40">
-        <v>-18.37604401027445</v>
+        <v>-15.73940687318632</v>
       </c>
       <c r="F40">
-        <v>5.980869658315716</v>
+        <v>7.872390293624997</v>
       </c>
       <c r="G40">
-        <v>-7.891441000380337</v>
+        <v>-8.916051211864067</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.905416619657982</v>
       </c>
       <c r="E41">
-        <v>-15.40002305656663</v>
+        <v>-15.60117969387338</v>
       </c>
       <c r="F41">
-        <v>6.400484136408222</v>
+        <v>7.631837370056437</v>
       </c>
       <c r="G41">
-        <v>-8.272758523124571</v>
+        <v>-8.712379194077545</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.797554649084814</v>
       </c>
       <c r="E42">
-        <v>-15.31744060258374</v>
+        <v>-14.74311377452983</v>
       </c>
       <c r="F42">
-        <v>6.271210776262137</v>
+        <v>7.978572084050643</v>
       </c>
       <c r="G42">
-        <v>-8.433152227824205</v>
+        <v>-9.616000974347607</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.672384512824242</v>
       </c>
       <c r="E43">
-        <v>-15.09873664742959</v>
+        <v>-14.53577715877174</v>
       </c>
       <c r="F43">
-        <v>5.900395421868549</v>
+        <v>8.083234648659555</v>
       </c>
       <c r="G43">
-        <v>-7.622899811738424</v>
+        <v>-9.541530790258395</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.536338614933724</v>
       </c>
       <c r="E44">
-        <v>-14.22476392871195</v>
+        <v>-13.28650780510861</v>
       </c>
       <c r="F44">
-        <v>6.201775363824677</v>
+        <v>8.056993626073671</v>
       </c>
       <c r="G44">
-        <v>-8.312909164191302</v>
+        <v>-10.01944064138464</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.389599171324914</v>
       </c>
       <c r="E45">
-        <v>-13.37587245318495</v>
+        <v>-12.49008800145949</v>
       </c>
       <c r="F45">
-        <v>6.441581099995911</v>
+        <v>8.508304754466899</v>
       </c>
       <c r="G45">
-        <v>-7.805001857713168</v>
+        <v>-10.42757964868567</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.237245227878514</v>
       </c>
       <c r="E46">
-        <v>-13.19524929266815</v>
+        <v>-12.59956665198197</v>
       </c>
       <c r="F46">
-        <v>5.926896551818912</v>
+        <v>8.132206072778256</v>
       </c>
       <c r="G46">
-        <v>-8.888524826267663</v>
+        <v>-10.29762592054612</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.076250409218377</v>
       </c>
       <c r="E47">
-        <v>-13.01038570338871</v>
+        <v>-12.4007482726511</v>
       </c>
       <c r="F47">
-        <v>6.141047749525445</v>
+        <v>8.034561436805861</v>
       </c>
       <c r="G47">
-        <v>-9.217893753137924</v>
+        <v>-10.38030428562979</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.904144573379247</v>
       </c>
       <c r="E48">
-        <v>-12.60078354290014</v>
+        <v>-10.78650301418469</v>
       </c>
       <c r="F48">
-        <v>6.051509516956846</v>
+        <v>8.267925788052928</v>
       </c>
       <c r="G48">
-        <v>-7.610806842792388</v>
+        <v>-10.04112418058613</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.71971482763979</v>
       </c>
       <c r="E49">
-        <v>-11.5778019082703</v>
+        <v>-11.27117446936954</v>
       </c>
       <c r="F49">
-        <v>6.273883089503569</v>
+        <v>8.083126960897191</v>
       </c>
       <c r="G49">
-        <v>-8.475033792554846</v>
+        <v>-10.73844492326642</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.516886060962582</v>
       </c>
       <c r="E50">
-        <v>-10.22481856140356</v>
+        <v>-10.82651505208809</v>
       </c>
       <c r="F50">
-        <v>5.650803353200642</v>
+        <v>7.946739581495864</v>
       </c>
       <c r="G50">
-        <v>-7.949762423801217</v>
+        <v>-10.61319314613546</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.296249365604873</v>
       </c>
       <c r="E51">
-        <v>-9.546557619945808</v>
+        <v>-10.6034543782542</v>
       </c>
       <c r="F51">
-        <v>5.507207520660153</v>
+        <v>7.809005276697584</v>
       </c>
       <c r="G51">
-        <v>-9.409831779359687</v>
+        <v>-11.42961866780693</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.055180058347799</v>
       </c>
       <c r="E52">
-        <v>-11.06660389235378</v>
+        <v>-9.121322772030588</v>
       </c>
       <c r="F52">
-        <v>6.405692910637026</v>
+        <v>7.958384770444419</v>
       </c>
       <c r="G52">
-        <v>-10.16973729137814</v>
+        <v>-10.83846907541345</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.794083157504129</v>
       </c>
       <c r="E53">
-        <v>-10.84748461606715</v>
+        <v>-9.252207073721236</v>
       </c>
       <c r="F53">
-        <v>6.562577413053224</v>
+        <v>8.097192639396727</v>
       </c>
       <c r="G53">
-        <v>-9.564757279513236</v>
+        <v>-11.72241367370029</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.516370719217928</v>
       </c>
       <c r="E54">
-        <v>-8.937547324118251</v>
+        <v>-7.911097758032176</v>
       </c>
       <c r="F54">
-        <v>5.733421404486253</v>
+        <v>7.871283594774857</v>
       </c>
       <c r="G54">
-        <v>-9.570366464267243</v>
+        <v>-11.20188080637953</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.222900869874768</v>
       </c>
       <c r="E55">
-        <v>-8.623589467229161</v>
+        <v>-8.034581037141978</v>
       </c>
       <c r="F55">
-        <v>6.491626088268641</v>
+        <v>7.917146984398254</v>
       </c>
       <c r="G55">
-        <v>-9.759452252023213</v>
+        <v>-11.86367845278084</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.920610052379076</v>
       </c>
       <c r="E56">
-        <v>-9.102820215578477</v>
+        <v>-7.382298432521031</v>
       </c>
       <c r="F56">
-        <v>5.299663381358348</v>
+        <v>7.915975672890696</v>
       </c>
       <c r="G56">
-        <v>-9.856911347609472</v>
+        <v>-11.63924318326119</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.613844073775807</v>
       </c>
       <c r="E57">
-        <v>-9.731350604632729</v>
+        <v>-7.194913843967417</v>
       </c>
       <c r="F57">
-        <v>5.695135919863666</v>
+        <v>7.900657502878127</v>
       </c>
       <c r="G57">
-        <v>-9.698176771097488</v>
+        <v>-11.35938833293369</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.30682313964165</v>
       </c>
       <c r="E58">
-        <v>-7.080289364613474</v>
+        <v>-6.997146227101731</v>
       </c>
       <c r="F58">
-        <v>5.880696845029977</v>
+        <v>7.787162885020567</v>
       </c>
       <c r="G58">
-        <v>-10.79396110162415</v>
+        <v>-12.08244579579318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.00395628579555</v>
       </c>
       <c r="E59">
-        <v>-8.563118710339658</v>
+        <v>-6.929507027465574</v>
       </c>
       <c r="F59">
-        <v>6.17489981180825</v>
+        <v>7.925988978055736</v>
       </c>
       <c r="G59">
-        <v>-10.92214343955863</v>
+        <v>-12.13422730401332</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.70418995892155</v>
       </c>
       <c r="E60">
-        <v>-9.921397401645558</v>
+        <v>-6.395312680443477</v>
       </c>
       <c r="F60">
-        <v>5.758492772299383</v>
+        <v>8.167303999634871</v>
       </c>
       <c r="G60">
-        <v>-10.24466957725998</v>
+        <v>-12.86511177915696</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.4087833127900241</v>
       </c>
       <c r="E61">
-        <v>-7.656011671672531</v>
+        <v>-5.683925725458895</v>
       </c>
       <c r="F61">
-        <v>5.882002352056789</v>
+        <v>7.933489016520682</v>
       </c>
       <c r="G61">
-        <v>-10.99628075371247</v>
+        <v>-12.49377121686766</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.1166988488370625</v>
       </c>
       <c r="E62">
-        <v>-7.210936933258605</v>
+        <v>-6.599052615194266</v>
       </c>
       <c r="F62">
-        <v>6.306974710510603</v>
+        <v>7.690853577301485</v>
       </c>
       <c r="G62">
-        <v>-10.40671588328579</v>
+        <v>-12.76333712276159</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.1738865766158626</v>
       </c>
       <c r="E63">
-        <v>-7.313085165792764</v>
+        <v>-5.605263902966643</v>
       </c>
       <c r="F63">
-        <v>5.577467987030801</v>
+        <v>7.79548466394909</v>
       </c>
       <c r="G63">
-        <v>-11.15051179580479</v>
+        <v>-12.8106921135275</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4617388232991957</v>
       </c>
       <c r="E64">
-        <v>-6.198666430635495</v>
+        <v>-5.943904294759188</v>
       </c>
       <c r="F64">
-        <v>5.291228944463043</v>
+        <v>7.68828066814839</v>
       </c>
       <c r="G64">
-        <v>-11.6018129380584</v>
+        <v>-13.16644522523555</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7482562244827831</v>
       </c>
       <c r="E65">
-        <v>-4.562022903494286</v>
+        <v>-4.984603849372941</v>
       </c>
       <c r="F65">
-        <v>5.445469298129506</v>
+        <v>7.749995696391759</v>
       </c>
       <c r="G65">
-        <v>-11.99343506970376</v>
+        <v>-12.79959122752608</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.031184203139369</v>
       </c>
       <c r="E66">
-        <v>-6.434693430225501</v>
+        <v>-6.193537214649332</v>
       </c>
       <c r="F66">
-        <v>5.469375981374299</v>
+        <v>7.792249060873756</v>
       </c>
       <c r="G66">
-        <v>-12.00116548443805</v>
+        <v>-12.82586053960187</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.308143468794176</v>
       </c>
       <c r="E67">
-        <v>-6.369155755519706</v>
+        <v>-6.092859218924163</v>
       </c>
       <c r="F67">
-        <v>5.859440937474142</v>
+        <v>7.441940769903873</v>
       </c>
       <c r="G67">
-        <v>-11.29758548160056</v>
+        <v>-12.83678911646026</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.578355239243005</v>
       </c>
       <c r="E68">
-        <v>-7.037702335688682</v>
+        <v>-5.632953362869275</v>
       </c>
       <c r="F68">
-        <v>5.619235928214758</v>
+        <v>7.555443671435461</v>
       </c>
       <c r="G68">
-        <v>-11.64944597312326</v>
+        <v>-13.70651951582079</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.838001228718803</v>
       </c>
       <c r="E69">
-        <v>-6.807722411787626</v>
+        <v>-5.739022226894071</v>
       </c>
       <c r="F69">
-        <v>5.973260275353599</v>
+        <v>7.911101559092623</v>
       </c>
       <c r="G69">
-        <v>-11.89028585628117</v>
+        <v>-13.56059716838969</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.086895500165841</v>
       </c>
       <c r="E70">
-        <v>-5.032801866797576</v>
+        <v>-5.333963679594868</v>
       </c>
       <c r="F70">
-        <v>5.102705777464321</v>
+        <v>7.715633359788829</v>
       </c>
       <c r="G70">
-        <v>-12.36392061313946</v>
+        <v>-13.35082514586604</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.323343848937986</v>
       </c>
       <c r="E71">
-        <v>-5.435505543275601</v>
+        <v>-5.819656824765617</v>
       </c>
       <c r="F71">
-        <v>5.740329988625601</v>
+        <v>7.722979321916855</v>
       </c>
       <c r="G71">
-        <v>-11.7158881175948</v>
+        <v>-13.24632226137296</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.545838457990762</v>
       </c>
       <c r="E72">
-        <v>-6.170470278951234</v>
+        <v>-5.128583226370772</v>
       </c>
       <c r="F72">
-        <v>5.431764787817591</v>
+        <v>7.854056866266238</v>
       </c>
       <c r="G72">
-        <v>-12.5115060048751</v>
+        <v>-13.59492584901824</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.756198018505818</v>
       </c>
       <c r="E73">
-        <v>-6.725343465159652</v>
+        <v>-5.369511015324075</v>
       </c>
       <c r="F73">
-        <v>5.005892822364337</v>
+        <v>7.834505738825364</v>
       </c>
       <c r="G73">
-        <v>-11.94199556902505</v>
+        <v>-13.33780536259016</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.953145034454345</v>
       </c>
       <c r="E74">
-        <v>-6.875606650891949</v>
+        <v>-5.305078094830685</v>
       </c>
       <c r="F74">
-        <v>5.252701576558839</v>
+        <v>7.674205049240021</v>
       </c>
       <c r="G74">
-        <v>-11.9907486135195</v>
+        <v>-13.23328289751264</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.138645045803379</v>
       </c>
       <c r="E75">
-        <v>-8.676364323533758</v>
+        <v>-6.35140493031739</v>
       </c>
       <c r="F75">
-        <v>5.968835136687844</v>
+        <v>7.834224093908412</v>
       </c>
       <c r="G75">
-        <v>-10.91970108799364</v>
+        <v>-13.75322312581122</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.312148461324624</v>
       </c>
       <c r="E76">
-        <v>-8.665428918115484</v>
+        <v>-6.081205307946695</v>
       </c>
       <c r="F76">
-        <v>5.917345475664633</v>
+        <v>7.618725970804927</v>
       </c>
       <c r="G76">
-        <v>-12.4291291807917</v>
+        <v>-13.21197400015997</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.470498135848071</v>
       </c>
       <c r="E77">
-        <v>-8.526603676371765</v>
+        <v>-7.08291004095944</v>
       </c>
       <c r="F77">
-        <v>5.695997421962577</v>
+        <v>7.90680730247651</v>
       </c>
       <c r="G77">
-        <v>-11.44317887521318</v>
+        <v>-13.0837603332904</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.611461474399768</v>
       </c>
       <c r="E78">
-        <v>-8.133431619884222</v>
+        <v>-7.503597122473973</v>
       </c>
       <c r="F78">
-        <v>5.715300039182611</v>
+        <v>7.556525519263517</v>
       </c>
       <c r="G78">
-        <v>-11.42561117485957</v>
+        <v>-13.14567936275783</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.7279431568088</v>
       </c>
       <c r="E79">
-        <v>-8.606033842959111</v>
+        <v>-8.582622190721052</v>
       </c>
       <c r="F79">
-        <v>5.255340755104157</v>
+        <v>7.809124561603587</v>
       </c>
       <c r="G79">
-        <v>-10.42007636873081</v>
+        <v>-12.7701485553998</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.8148750383715</v>
       </c>
       <c r="E80">
-        <v>-8.850678756048136</v>
+        <v>-7.898592438733116</v>
       </c>
       <c r="F80">
-        <v>5.796364073220571</v>
+        <v>8.019576270489219</v>
       </c>
       <c r="G80">
-        <v>-10.93663959890078</v>
+        <v>-12.81712237745541</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.866543467717482</v>
       </c>
       <c r="E81">
-        <v>-10.67356473862863</v>
+        <v>-9.350887374799161</v>
       </c>
       <c r="F81">
-        <v>5.633800283890779</v>
+        <v>8.099392783218562</v>
       </c>
       <c r="G81">
-        <v>-10.74436087050988</v>
+        <v>-12.72793542610609</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.873878336013461</v>
       </c>
       <c r="E82">
-        <v>-10.91810166822321</v>
+        <v>-9.365764177764698</v>
       </c>
       <c r="F82">
-        <v>5.710641300909267</v>
+        <v>7.664370671433985</v>
       </c>
       <c r="G82">
-        <v>-10.95823828890306</v>
+        <v>-11.89009788267061</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.829157929199794</v>
       </c>
       <c r="E83">
-        <v>-10.38770750956333</v>
+        <v>-10.599155804533</v>
       </c>
       <c r="F83">
-        <v>6.171392504224797</v>
+        <v>8.492448145642511</v>
       </c>
       <c r="G83">
-        <v>-11.02662674346728</v>
+        <v>-12.1908125822811</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.722851853385978</v>
       </c>
       <c r="E84">
-        <v>-12.69037661759935</v>
+        <v>-11.60916696019541</v>
       </c>
       <c r="F84">
-        <v>5.512795687159438</v>
+        <v>8.197039075925762</v>
       </c>
       <c r="G84">
-        <v>-10.10848269640915</v>
+        <v>-11.45314800343434</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.548610015835518</v>
       </c>
       <c r="E85">
-        <v>-13.36051387770573</v>
+        <v>-12.65837612434154</v>
       </c>
       <c r="F85">
-        <v>6.018089862458304</v>
+        <v>8.459792245889348</v>
       </c>
       <c r="G85">
-        <v>-9.345818932730181</v>
+        <v>-11.96944232691143</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.304901403675589</v>
       </c>
       <c r="E86">
-        <v>-14.77734869548039</v>
+        <v>-12.25053077224338</v>
       </c>
       <c r="F86">
-        <v>5.633490474482132</v>
+        <v>8.401821438306634</v>
       </c>
       <c r="G86">
-        <v>-10.17279577866663</v>
+        <v>-12.03539495677213</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.991524880949567</v>
       </c>
       <c r="E87">
-        <v>-16.15611933146299</v>
+        <v>-14.06822108745651</v>
       </c>
       <c r="F87">
-        <v>5.344249428446629</v>
+        <v>8.069574870187392</v>
       </c>
       <c r="G87">
-        <v>-10.31121484614287</v>
+        <v>-11.43205710325503</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.616573198280071</v>
       </c>
       <c r="E88">
-        <v>-17.66087347977295</v>
+        <v>-15.21679167933785</v>
       </c>
       <c r="F88">
-        <v>5.315443780381679</v>
+        <v>8.650828679588164</v>
       </c>
       <c r="G88">
-        <v>-10.07261889796102</v>
+        <v>-11.42990323896736</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.191635388849698</v>
       </c>
       <c r="E89">
-        <v>-18.34834624394917</v>
+        <v>-16.74773597826217</v>
       </c>
       <c r="F89">
-        <v>5.962446767277455</v>
+        <v>8.476483849055759</v>
       </c>
       <c r="G89">
-        <v>-10.16550527439595</v>
+        <v>-11.03227639476245</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.732410283310323</v>
       </c>
       <c r="E90">
-        <v>-21.43021594148156</v>
+        <v>-18.35308921128212</v>
       </c>
       <c r="F90">
-        <v>5.68842614390099</v>
+        <v>8.717494031430663</v>
       </c>
       <c r="G90">
-        <v>-9.493316864522011</v>
+        <v>-10.49394869230866</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.259614720946165</v>
       </c>
       <c r="E91">
-        <v>-22.42927092566907</v>
+        <v>-19.0330612758057</v>
       </c>
       <c r="F91">
-        <v>5.883640862779527</v>
+        <v>8.404127613156028</v>
       </c>
       <c r="G91">
-        <v>-9.583792218327043</v>
+        <v>-10.2736318723815</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7910292314242782</v>
       </c>
       <c r="E92">
-        <v>-24.51227253352357</v>
+        <v>-22.3104433964544</v>
       </c>
       <c r="F92">
-        <v>5.94452586688529</v>
+        <v>8.327566584319685</v>
       </c>
       <c r="G92">
-        <v>-8.564494872086229</v>
+        <v>-10.85597020177998</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.3474316770049086</v>
       </c>
       <c r="E93">
-        <v>-25.79695216694219</v>
+        <v>-24.33752616703141</v>
       </c>
       <c r="F93">
-        <v>6.001761084214319</v>
+        <v>8.521338287182546</v>
       </c>
       <c r="G93">
-        <v>-9.14299279619118</v>
+        <v>-10.05667769148769</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.0555340694353088</v>
       </c>
       <c r="E94">
-        <v>-28.51587272679782</v>
+        <v>-26.31409758147586</v>
       </c>
       <c r="F94">
-        <v>5.765749270747906</v>
+        <v>8.368136706239195</v>
       </c>
       <c r="G94">
-        <v>-9.894912040505421</v>
+        <v>-9.468181920971068</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.4074770934235939</v>
       </c>
       <c r="E95">
-        <v>-28.95995900091643</v>
+        <v>-28.22336620640147</v>
       </c>
       <c r="F95">
-        <v>5.685868145361145</v>
+        <v>8.348423218787373</v>
       </c>
       <c r="G95">
-        <v>-8.029905755886917</v>
+        <v>-9.218774879437426</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.7003139450393382</v>
       </c>
       <c r="E96">
-        <v>-32.53633911126219</v>
+        <v>-30.03103274608213</v>
       </c>
       <c r="F96">
-        <v>5.476660644314518</v>
+        <v>8.234126741283902</v>
       </c>
       <c r="G96">
-        <v>-7.90727777707003</v>
+        <v>-9.503785950332375</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9367720826453286</v>
       </c>
       <c r="E97">
-        <v>-34.24686203805511</v>
+        <v>-32.79922077527853</v>
       </c>
       <c r="F97">
-        <v>5.247406652120144</v>
+        <v>7.574073654324422</v>
       </c>
       <c r="G97">
-        <v>-8.317541930468233</v>
+        <v>-9.007642658981798</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.119281925484332</v>
       </c>
       <c r="E98">
-        <v>-37.21165478494625</v>
+        <v>-35.37665596153689</v>
       </c>
       <c r="F98">
-        <v>4.860226071316849</v>
+        <v>7.683974814388637</v>
       </c>
       <c r="G98">
-        <v>-7.576190980258817</v>
+        <v>-8.648722714084727</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.260919833796205</v>
       </c>
       <c r="E99">
-        <v>-38.55577517884581</v>
+        <v>-36.91904651087244</v>
       </c>
       <c r="F99">
-        <v>4.383843575110493</v>
+        <v>7.353166292080656</v>
       </c>
       <c r="G99">
-        <v>-7.739948629364102</v>
+        <v>-8.431662798034976</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.372033701784699</v>
       </c>
       <c r="E100">
-        <v>-41.45298064124236</v>
+        <v>-40.36807047254799</v>
       </c>
       <c r="F100">
-        <v>4.58537873727239</v>
+        <v>7.069225140688263</v>
       </c>
       <c r="G100">
-        <v>-8.299594366776624</v>
+        <v>-7.480021592500568</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.47173449225166</v>
       </c>
       <c r="E101">
-        <v>-44.78161961945643</v>
+        <v>-42.95437691819618</v>
       </c>
       <c r="F101">
-        <v>4.438449554303037</v>
+        <v>6.591127923958112</v>
       </c>
       <c r="G101">
-        <v>-8.274029955740442</v>
+        <v>-7.736913638776933</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.562684027254605</v>
       </c>
       <c r="E102">
-        <v>-47.5431022889689</v>
+        <v>-45.17512600945562</v>
       </c>
       <c r="F102">
-        <v>3.881296266119311</v>
+        <v>6.486455418940366</v>
       </c>
       <c r="G102">
-        <v>-7.133019696661928</v>
+        <v>-7.458010404852891</v>
       </c>
     </row>
   </sheetData>
